--- a/data_lake/fixed_income/South Korea/KOFR.xlsx
+++ b/data_lake/fixed_income/South Korea/KOFR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\fixed_income\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AC6F4C-CA80-427B-94AD-D051BA64AFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5E2531-2F4F-4D51-9449-34D4486C2483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="11">
   <si>
     <t>KOFR</t>
   </si>
@@ -13778,7 +13778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC83E2F-018C-4B5A-96A0-1EEF1FA8E943}">
-  <dimension ref="A1:F2103"/>
+  <dimension ref="A1:F2113"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
@@ -55848,6 +55848,200 @@
       </c>
       <c r="F2103" s="12">
         <v>1192.87995</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2104" s="9">
+        <v>46219</v>
+      </c>
+      <c r="B2104" s="9">
+        <v>46223</v>
+      </c>
+      <c r="C2104" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2104" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2104" s="11">
+        <v>2.7490000000000001</v>
+      </c>
+      <c r="F2104" s="12">
+        <v>1192.96316</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2105" s="9">
+        <v>46223</v>
+      </c>
+      <c r="B2105" s="9">
+        <v>46224</v>
+      </c>
+      <c r="C2105" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2105" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2105" s="11">
+        <v>2.698</v>
+      </c>
+      <c r="F2105" s="12">
+        <v>1193.3225500000001</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2106" s="9">
+        <v>46224</v>
+      </c>
+      <c r="B2106" s="9">
+        <v>46225</v>
+      </c>
+      <c r="C2106" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2106" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2106" s="11">
+        <v>2.6789999999999998</v>
+      </c>
+      <c r="F2106" s="12">
+        <v>1193.41076</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2107" s="9">
+        <v>46225</v>
+      </c>
+      <c r="B2107" s="9">
+        <v>46226</v>
+      </c>
+      <c r="C2107" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2107" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2107" s="11">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="F2107" s="12">
+        <v>1193.4983500000001</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2108" s="9">
+        <v>46226</v>
+      </c>
+      <c r="B2108" s="9">
+        <v>46227</v>
+      </c>
+      <c r="C2108" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2108" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2108" s="11">
+        <v>2.6680000000000001</v>
+      </c>
+      <c r="F2108" s="12">
+        <v>1193.5858499999999</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2109" s="9">
+        <v>46227</v>
+      </c>
+      <c r="B2109" s="9">
+        <v>46230</v>
+      </c>
+      <c r="C2109" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2109" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2109" s="11">
+        <v>2.6720000000000002</v>
+      </c>
+      <c r="F2109" s="12">
+        <v>1193.6731</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2110" s="9">
+        <v>46230</v>
+      </c>
+      <c r="B2110" s="9">
+        <v>46231</v>
+      </c>
+      <c r="C2110" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2110" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2110" s="11">
+        <v>2.6819999999999999</v>
+      </c>
+      <c r="F2110" s="12">
+        <v>1193.93525</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2111" s="9">
+        <v>46231</v>
+      </c>
+      <c r="B2111" s="9">
+        <v>46232</v>
+      </c>
+      <c r="C2111" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2111" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2111" s="11">
+        <v>2.677</v>
+      </c>
+      <c r="F2111" s="12">
+        <v>1194.02298</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2112" s="9">
+        <v>46232</v>
+      </c>
+      <c r="B2112" s="9">
+        <v>46233</v>
+      </c>
+      <c r="C2112" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2112" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2112" s="11">
+        <v>2.6739999999999999</v>
+      </c>
+      <c r="F2112" s="12">
+        <v>1194.1105500000001</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2113" s="9">
+        <v>46233</v>
+      </c>
+      <c r="B2113" s="9">
+        <v>46234</v>
+      </c>
+      <c r="C2113" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2113" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
